--- a/artfynd/A 19686-2026 artfynd.xlsx
+++ b/artfynd/A 19686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,685 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133029653</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>455972</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6778399</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133030066</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>456075</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6778436</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133030123</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>456046</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6778459</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133029956</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>455989</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6778386</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133030196</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>455987</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6778365</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133030028</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>456087</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6778409</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133029999</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>456076</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6778439</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19686-2026 artfynd.xlsx
+++ b/artfynd/A 19686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133029999</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030028</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133029956</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030196</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124075611</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030066</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1510,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030175</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030250</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,6 +1714,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030264</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1761,8 +1816,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133029653</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>